--- a/artfynd/A 31727-2021 artfynd.xlsx
+++ b/artfynd/A 31727-2021 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>125748465</v>
       </c>
       <c r="B4" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31727-2021 artfynd.xlsx
+++ b/artfynd/A 31727-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125748463</v>
       </c>
       <c r="B2" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>125748460</v>
       </c>
       <c r="B3" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>125748465</v>
       </c>
       <c r="B4" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>125748464</v>
       </c>
       <c r="B5" t="n">
-        <v>80106</v>
+        <v>80107</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31727-2021 artfynd.xlsx
+++ b/artfynd/A 31727-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125748463</v>
       </c>
       <c r="B2" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>125748460</v>
       </c>
       <c r="B3" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>125748465</v>
       </c>
       <c r="B4" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>125748464</v>
       </c>
       <c r="B5" t="n">
-        <v>80107</v>
+        <v>80111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31727-2021 artfynd.xlsx
+++ b/artfynd/A 31727-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125748463</v>
       </c>
       <c r="B2" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>125748460</v>
       </c>
       <c r="B3" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>125748465</v>
       </c>
       <c r="B4" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>125748464</v>
       </c>
       <c r="B5" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31727-2021 artfynd.xlsx
+++ b/artfynd/A 31727-2021 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>125748465</v>
       </c>
       <c r="B4" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31727-2021 artfynd.xlsx
+++ b/artfynd/A 31727-2021 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>125748465</v>
       </c>
       <c r="B4" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31727-2021 artfynd.xlsx
+++ b/artfynd/A 31727-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125748463</v>
       </c>
       <c r="B2" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>125748460</v>
       </c>
       <c r="B3" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>125748465</v>
       </c>
       <c r="B4" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>125748464</v>
       </c>
       <c r="B5" t="n">
-        <v>80112</v>
+        <v>80116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31727-2021 artfynd.xlsx
+++ b/artfynd/A 31727-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125748463</v>
+        <v>125748465</v>
       </c>
       <c r="B2" t="n">
-        <v>80080</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534103</v>
+        <v>534098</v>
       </c>
       <c r="R2" t="n">
-        <v>7014702</v>
+        <v>7014689</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,32 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125748460</v>
+        <v>125748462</v>
       </c>
       <c r="B3" t="n">
-        <v>80080</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534070</v>
+        <v>534078</v>
       </c>
       <c r="R3" t="n">
-        <v>7014702</v>
+        <v>7014755</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125748465</v>
+        <v>125748460</v>
       </c>
       <c r="B4" t="n">
-        <v>91242</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534098</v>
+        <v>534070</v>
       </c>
       <c r="R4" t="n">
-        <v>7014689</v>
+        <v>7014702</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,32 +1008,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125748464</v>
+        <v>125748463</v>
       </c>
       <c r="B5" t="n">
-        <v>80116</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534109</v>
+        <v>534103</v>
       </c>
       <c r="R5" t="n">
-        <v>7014710</v>
+        <v>7014702</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,6 +1116,117 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125748464</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Risholmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>534109</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7014710</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
